--- a/data/gravel/Doppo by Simworks High Plains Drifter 2025.xlsx
+++ b/data/gravel/Doppo by Simworks High Plains Drifter 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D92B99C-0C8E-BE4D-BEFE-CC987E871675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0641CD9-D22F-5C44-BA12-CF0BC080C1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15320" yWindow="500" windowWidth="24160" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4640" yWindow="500" windowWidth="24160" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -266,9 +266,6 @@
     <t>Doppo by Simworks</t>
   </si>
   <si>
-    <t>Ronin</t>
-  </si>
-  <si>
     <t>Fork Length (Axle to Crown) (mm)</t>
   </si>
   <si>
@@ -381,6 +378,9 @@
   </si>
   <si>
     <t>external</t>
+  </si>
+  <si>
+    <t>High Plains Drifter</t>
   </si>
 </sst>
 </file>
@@ -753,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -777,7 +777,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -785,7 +785,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="22" x14ac:dyDescent="0.3">
@@ -793,16 +793,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
         <v>84</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>85</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>87</v>
       </c>
       <c r="F8" t="s">
         <v>70</v>
@@ -830,7 +830,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9">
         <v>480</v>
@@ -869,7 +869,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10">
         <v>560</v>
@@ -884,7 +884,7 @@
         <v>635</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J10">
         <f>C11</f>
@@ -908,7 +908,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11">
         <v>55</v>
@@ -923,7 +923,7 @@
         <v>55</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J11">
         <f>C13</f>
@@ -947,7 +947,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C12">
         <v>440</v>
@@ -962,7 +962,7 @@
         <v>440</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <f>C21</f>
@@ -986,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13">
         <v>69</v>
@@ -1001,7 +1001,7 @@
         <v>70.5</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J13">
         <f>C22</f>
@@ -1025,7 +1025,7 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C14">
         <v>74</v>
@@ -1040,7 +1040,7 @@
         <v>72.5</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J14" s="2">
         <v>10</v>
@@ -1060,7 +1060,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15">
         <v>562</v>
@@ -1080,7 +1080,7 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16">
         <v>395</v>
@@ -1095,7 +1095,7 @@
         <v>437</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J16">
         <f>J11*PI()/180</f>
@@ -1119,7 +1119,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17">
         <v>811</v>
@@ -1134,7 +1134,7 @@
         <v>870</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J17">
         <f>J14*SIN(J16)</f>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C18">
         <v>800</v>
@@ -1173,7 +1173,7 @@
         <v>857</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J18">
         <f>ATAN(J13/J12)</f>
@@ -1213,7 +1213,7 @@
         <v>187.69222752183722</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J19">
         <f>J18 + ( PI()/2 - J16)</f>
@@ -1237,7 +1237,7 @@
         <v>13</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J20">
         <f>COS(J19)*J12</f>
@@ -1261,7 +1261,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="2">
         <v>430</v>
@@ -1276,7 +1276,7 @@
         <v>430</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J21">
         <f>J9-J10-J17-J20</f>
@@ -1315,7 +1315,7 @@
         <v>55</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J22">
         <f>J21/SIN(J16)</f>
@@ -1344,7 +1344,7 @@
         <v>23</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -1352,7 +1352,7 @@
         <v>18</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J25">
         <f>ACOS(J13/J12)</f>
@@ -1376,7 +1376,7 @@
         <v>20</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J26">
         <f>PI()/2 - J16</f>
@@ -1400,7 +1400,7 @@
         <v>19</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J27">
         <f>J25-J26</f>
@@ -1436,7 +1436,7 @@
         <v>700</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J28">
         <f>J12*SIN(J27)</f>
@@ -1472,10 +1472,10 @@
         <v>2.4</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J29">
         <f>J9-J28-J17-J10</f>
@@ -1511,7 +1511,7 @@
         <v>2.4</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J30">
         <f>J29/SIN(J16)</f>
@@ -1561,7 +1561,7 @@
         <v>68</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1648,7 +1648,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1700,7 +1700,7 @@
         <v>52</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1708,7 +1708,7 @@
         <v>53</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Doppo by Simworks High Plains Drifter 2025.xlsx
+++ b/data/gravel/Doppo by Simworks High Plains Drifter 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0641CD9-D22F-5C44-BA12-CF0BC080C1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8058D25D-F368-2742-835B-089866EE36EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="500" windowWidth="24160" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>High Plains Drifter</t>
+  </si>
+  <si>
+    <t>https://www.sim.works/cdn/shop/files/Doppo-1-2_900x.jpg?v=1757634171</t>
   </si>
 </sst>
 </file>
@@ -780,6 +783,11 @@
         <v>80</v>
       </c>
     </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Doppo by Simworks High Plains Drifter 2025.xlsx
+++ b/data/gravel/Doppo by Simworks High Plains Drifter 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8058D25D-F368-2742-835B-089866EE36EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC50D7B-8358-8D48-BEA2-D86C6C36873B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="500" windowWidth="24160" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -384,6 +384,12 @@
   </si>
   <si>
     <t>https://www.sim.works/cdn/shop/files/Doppo-1-2_900x.jpg?v=1757634171</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Nagoya, Japan</t>
   </si>
 </sst>
 </file>
@@ -737,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1803,6 +1809,14 @@
         <v>75</v>
       </c>
     </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>117</v>
+      </c>
+      <c r="B73" t="s">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Doppo by Simworks High Plains Drifter 2025.xlsx
+++ b/data/gravel/Doppo by Simworks High Plains Drifter 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC50D7B-8358-8D48-BEA2-D86C6C36873B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C604A931-AD56-4A4F-AB46-9B8326B8AB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="500" windowWidth="24160" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -390,6 +390,24 @@
   </si>
   <si>
     <t>Nagoya, Japan</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -743,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1659,161 +1677,191 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51">
-        <v>31.6</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="2"/>
+        <v>122</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B57">
+        <v>31.6</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>114</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B58" s="2"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" s="2"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65">
-        <v>3</v>
+        <v>53</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B66" s="2"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" s="2"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69">
-        <v>2800</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>57</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B70" s="2"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="B71">
+        <v>3</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>66</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B72" s="2"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="2"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="2"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75">
+        <v>2800</v>
+      </c>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="2"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>117</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>118</v>
       </c>
     </row>
